--- a/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_us_crime.xlsx
+++ b/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_us_crime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos_D\etapa-analisis_pcsmote\datasets\datasets_aumentados\logs\pcsmote\por_muestras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D6C3F7-0F11-4B82-8639-68AB528A0230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75960DBE-3E21-4047-B21A-F3BAE56E134A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -157,12 +157,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -192,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -200,6 +206,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,6 +520,8 @@
   <cols>
     <col min="1" max="1" width="39.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="4"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -528,13 +540,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -9691,13 +9703,13 @@
       <c r="E120">
         <v>7</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G120">
         <v>0.45</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I120">
@@ -9768,13 +9780,13 @@
       <c r="E121">
         <v>7</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G121">
         <v>0.45</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I121">
@@ -9845,13 +9857,13 @@
       <c r="E122">
         <v>7</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G122">
         <v>0.45</v>
       </c>
-      <c r="H122">
+      <c r="H122" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I122">
@@ -9922,13 +9934,13 @@
       <c r="E123">
         <v>7</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G123">
         <v>0.45</v>
       </c>
-      <c r="H123">
+      <c r="H123" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I123">
@@ -9983,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>26</v>
       </c>
@@ -9999,13 +10011,13 @@
       <c r="E124">
         <v>7</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G124">
         <v>0.45</v>
       </c>
-      <c r="H124">
+      <c r="H124" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I124">
@@ -10076,13 +10088,13 @@
       <c r="E125">
         <v>7</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G125">
         <v>0.45</v>
       </c>
-      <c r="H125">
+      <c r="H125" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I125">
@@ -10153,13 +10165,13 @@
       <c r="E126">
         <v>7</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G126">
         <v>0.45</v>
       </c>
-      <c r="H126">
+      <c r="H126" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I126">
@@ -10230,13 +10242,13 @@
       <c r="E127">
         <v>7</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G127">
         <v>0.45</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I127">
@@ -10307,13 +10319,13 @@
       <c r="E128">
         <v>7</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G128">
         <v>0.45</v>
       </c>
-      <c r="H128">
+      <c r="H128" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I128">
@@ -10384,13 +10396,13 @@
       <c r="E129">
         <v>7</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G129">
         <v>0.45</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I129">
@@ -10445,7 +10457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>26</v>
       </c>
@@ -10461,13 +10473,13 @@
       <c r="E130">
         <v>7</v>
       </c>
-      <c r="F130">
+      <c r="F130" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G130">
         <v>0.45</v>
       </c>
-      <c r="H130">
+      <c r="H130" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I130">
@@ -10538,13 +10550,13 @@
       <c r="E131">
         <v>7</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G131">
         <v>0.45</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I131">
@@ -10599,7 +10611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>26</v>
       </c>
@@ -10615,13 +10627,13 @@
       <c r="E132">
         <v>7</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G132">
         <v>0.45</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I132">
@@ -10692,13 +10704,13 @@
       <c r="E133">
         <v>7</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G133">
         <v>0.45</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I133">
@@ -10753,7 +10765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>26</v>
       </c>
@@ -10769,13 +10781,13 @@
       <c r="E134">
         <v>7</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G134">
         <v>0.45</v>
       </c>
-      <c r="H134">
+      <c r="H134" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I134">
@@ -10846,13 +10858,13 @@
       <c r="E135">
         <v>7</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G135">
         <v>0.45</v>
       </c>
-      <c r="H135">
+      <c r="H135" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I135">
@@ -10907,7 +10919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>26</v>
       </c>
@@ -10923,13 +10935,13 @@
       <c r="E136">
         <v>7</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G136">
         <v>0.45</v>
       </c>
-      <c r="H136">
+      <c r="H136" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I136">
@@ -11000,13 +11012,13 @@
       <c r="E137">
         <v>7</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G137">
         <v>0.45</v>
       </c>
-      <c r="H137">
+      <c r="H137" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I137">
@@ -11077,13 +11089,13 @@
       <c r="E138">
         <v>7</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G138">
         <v>0.45</v>
       </c>
-      <c r="H138">
+      <c r="H138" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I138">
@@ -11154,13 +11166,13 @@
       <c r="E139">
         <v>7</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G139">
         <v>0.45</v>
       </c>
-      <c r="H139">
+      <c r="H139" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I139">
@@ -11231,13 +11243,13 @@
       <c r="E140">
         <v>7</v>
       </c>
-      <c r="F140">
+      <c r="F140" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G140">
         <v>0.45</v>
       </c>
-      <c r="H140">
+      <c r="H140" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I140">
@@ -11308,13 +11320,13 @@
       <c r="E141">
         <v>7</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G141">
         <v>0.45</v>
       </c>
-      <c r="H141">
+      <c r="H141" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I141">
@@ -11385,13 +11397,13 @@
       <c r="E142">
         <v>7</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G142">
         <v>0.45</v>
       </c>
-      <c r="H142">
+      <c r="H142" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I142">
@@ -11462,13 +11474,13 @@
       <c r="E143">
         <v>7</v>
       </c>
-      <c r="F143">
+      <c r="F143" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G143">
         <v>0.45</v>
       </c>
-      <c r="H143">
+      <c r="H143" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I143">
@@ -11539,13 +11551,13 @@
       <c r="E144">
         <v>7</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G144">
         <v>0.45</v>
       </c>
-      <c r="H144">
+      <c r="H144" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I144">
@@ -11616,13 +11628,13 @@
       <c r="E145">
         <v>7</v>
       </c>
-      <c r="F145">
+      <c r="F145" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G145">
         <v>0.45</v>
       </c>
-      <c r="H145">
+      <c r="H145" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I145">
@@ -11693,13 +11705,13 @@
       <c r="E146">
         <v>7</v>
       </c>
-      <c r="F146">
+      <c r="F146" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G146">
         <v>0.45</v>
       </c>
-      <c r="H146">
+      <c r="H146" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I146">
@@ -11770,13 +11782,13 @@
       <c r="E147">
         <v>7</v>
       </c>
-      <c r="F147">
+      <c r="F147" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G147">
         <v>0.45</v>
       </c>
-      <c r="H147">
+      <c r="H147" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I147">
@@ -11831,7 +11843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>26</v>
       </c>
@@ -11847,13 +11859,13 @@
       <c r="E148">
         <v>7</v>
       </c>
-      <c r="F148">
+      <c r="F148" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G148">
         <v>0.45</v>
       </c>
-      <c r="H148">
+      <c r="H148" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I148">
@@ -11924,13 +11936,13 @@
       <c r="E149">
         <v>7</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G149">
         <v>0.45</v>
       </c>
-      <c r="H149">
+      <c r="H149" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I149">
@@ -12001,13 +12013,13 @@
       <c r="E150">
         <v>7</v>
       </c>
-      <c r="F150">
+      <c r="F150" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G150">
         <v>0.45</v>
       </c>
-      <c r="H150">
+      <c r="H150" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I150">
@@ -12078,13 +12090,13 @@
       <c r="E151">
         <v>7</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G151">
         <v>0.45</v>
       </c>
-      <c r="H151">
+      <c r="H151" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I151">
@@ -12139,7 +12151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>26</v>
       </c>
@@ -12155,13 +12167,13 @@
       <c r="E152">
         <v>7</v>
       </c>
-      <c r="F152">
+      <c r="F152" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G152">
         <v>0.45</v>
       </c>
-      <c r="H152">
+      <c r="H152" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I152">
@@ -12232,13 +12244,13 @@
       <c r="E153">
         <v>7</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G153">
         <v>0.45</v>
       </c>
-      <c r="H153">
+      <c r="H153" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I153">
@@ -12309,13 +12321,13 @@
       <c r="E154">
         <v>7</v>
       </c>
-      <c r="F154">
+      <c r="F154" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G154">
         <v>0.45</v>
       </c>
-      <c r="H154">
+      <c r="H154" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I154">
@@ -12386,13 +12398,13 @@
       <c r="E155">
         <v>7</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G155">
         <v>0.45</v>
       </c>
-      <c r="H155">
+      <c r="H155" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I155">
@@ -12463,13 +12475,13 @@
       <c r="E156">
         <v>7</v>
       </c>
-      <c r="F156">
+      <c r="F156" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G156">
         <v>0.45</v>
       </c>
-      <c r="H156">
+      <c r="H156" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I156">
@@ -12524,7 +12536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>26</v>
       </c>
@@ -12540,13 +12552,13 @@
       <c r="E157">
         <v>7</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G157">
         <v>0.45</v>
       </c>
-      <c r="H157">
+      <c r="H157" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I157">
@@ -12617,13 +12629,13 @@
       <c r="E158">
         <v>7</v>
       </c>
-      <c r="F158">
+      <c r="F158" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G158">
         <v>0.45</v>
       </c>
-      <c r="H158">
+      <c r="H158" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I158">
@@ -12694,13 +12706,13 @@
       <c r="E159">
         <v>7</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G159">
         <v>0.45</v>
       </c>
-      <c r="H159">
+      <c r="H159" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I159">
@@ -12771,13 +12783,13 @@
       <c r="E160">
         <v>7</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G160">
         <v>0.45</v>
       </c>
-      <c r="H160">
+      <c r="H160" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I160">
@@ -12848,13 +12860,13 @@
       <c r="E161">
         <v>7</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G161">
         <v>0.45</v>
       </c>
-      <c r="H161">
+      <c r="H161" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I161">
@@ -12925,13 +12937,13 @@
       <c r="E162">
         <v>7</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G162">
         <v>0.45</v>
       </c>
-      <c r="H162">
+      <c r="H162" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I162">
@@ -13002,13 +13014,13 @@
       <c r="E163">
         <v>7</v>
       </c>
-      <c r="F163">
+      <c r="F163" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G163">
         <v>0.45</v>
       </c>
-      <c r="H163">
+      <c r="H163" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I163">
@@ -13079,13 +13091,13 @@
       <c r="E164">
         <v>7</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G164">
         <v>0.45</v>
       </c>
-      <c r="H164">
+      <c r="H164" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I164">
@@ -13156,13 +13168,13 @@
       <c r="E165">
         <v>7</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G165">
         <v>0.45</v>
       </c>
-      <c r="H165">
+      <c r="H165" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I165">
@@ -13233,13 +13245,13 @@
       <c r="E166">
         <v>7</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G166">
         <v>0.45</v>
       </c>
-      <c r="H166">
+      <c r="H166" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I166">
@@ -13294,7 +13306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>26</v>
       </c>
@@ -13310,13 +13322,13 @@
       <c r="E167">
         <v>7</v>
       </c>
-      <c r="F167">
+      <c r="F167" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G167">
         <v>0.45</v>
       </c>
-      <c r="H167">
+      <c r="H167" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I167">
@@ -13371,7 +13383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>26</v>
       </c>
@@ -13387,13 +13399,13 @@
       <c r="E168">
         <v>7</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G168">
         <v>0.45</v>
       </c>
-      <c r="H168">
+      <c r="H168" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I168">
@@ -13464,13 +13476,13 @@
       <c r="E169">
         <v>7</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G169">
         <v>0.45</v>
       </c>
-      <c r="H169">
+      <c r="H169" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I169">
@@ -13541,13 +13553,13 @@
       <c r="E170">
         <v>7</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G170">
         <v>0.45</v>
       </c>
-      <c r="H170">
+      <c r="H170" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I170">
@@ -13618,13 +13630,13 @@
       <c r="E171">
         <v>7</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G171">
         <v>0.45</v>
       </c>
-      <c r="H171">
+      <c r="H171" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I171">
@@ -13695,13 +13707,13 @@
       <c r="E172">
         <v>7</v>
       </c>
-      <c r="F172">
+      <c r="F172" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G172">
         <v>0.45</v>
       </c>
-      <c r="H172">
+      <c r="H172" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I172">
@@ -13772,13 +13784,13 @@
       <c r="E173">
         <v>7</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G173">
         <v>0.45</v>
       </c>
-      <c r="H173">
+      <c r="H173" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I173">
@@ -13849,13 +13861,13 @@
       <c r="E174">
         <v>7</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G174">
         <v>0.45</v>
       </c>
-      <c r="H174">
+      <c r="H174" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I174">
@@ -13926,13 +13938,13 @@
       <c r="E175">
         <v>7</v>
       </c>
-      <c r="F175">
+      <c r="F175" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G175">
         <v>0.45</v>
       </c>
-      <c r="H175">
+      <c r="H175" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I175">
@@ -14003,13 +14015,13 @@
       <c r="E176">
         <v>7</v>
       </c>
-      <c r="F176">
+      <c r="F176" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G176">
         <v>0.45</v>
       </c>
-      <c r="H176">
+      <c r="H176" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I176">
@@ -14080,13 +14092,13 @@
       <c r="E177">
         <v>7</v>
       </c>
-      <c r="F177">
+      <c r="F177" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G177">
         <v>0.45</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I177">
@@ -14157,13 +14169,13 @@
       <c r="E178">
         <v>7</v>
       </c>
-      <c r="F178">
+      <c r="F178" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G178">
         <v>0.45</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I178">
@@ -14234,13 +14246,13 @@
       <c r="E179">
         <v>7</v>
       </c>
-      <c r="F179">
+      <c r="F179" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G179">
         <v>0.45</v>
       </c>
-      <c r="H179">
+      <c r="H179" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I179">
@@ -14311,13 +14323,13 @@
       <c r="E180">
         <v>7</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G180">
         <v>0.45</v>
       </c>
-      <c r="H180">
+      <c r="H180" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I180">
@@ -14388,13 +14400,13 @@
       <c r="E181">
         <v>7</v>
       </c>
-      <c r="F181">
+      <c r="F181" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G181">
         <v>0.45</v>
       </c>
-      <c r="H181">
+      <c r="H181" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I181">
@@ -14465,13 +14477,13 @@
       <c r="E182">
         <v>7</v>
       </c>
-      <c r="F182">
+      <c r="F182" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G182">
         <v>0.45</v>
       </c>
-      <c r="H182">
+      <c r="H182" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I182">
@@ -14542,13 +14554,13 @@
       <c r="E183">
         <v>7</v>
       </c>
-      <c r="F183">
+      <c r="F183" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G183">
         <v>0.45</v>
       </c>
-      <c r="H183">
+      <c r="H183" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I183">
@@ -14603,7 +14615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -14619,13 +14631,13 @@
       <c r="E184">
         <v>7</v>
       </c>
-      <c r="F184">
+      <c r="F184" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G184">
         <v>0.45</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I184">
@@ -14696,13 +14708,13 @@
       <c r="E185">
         <v>7</v>
       </c>
-      <c r="F185">
+      <c r="F185" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G185">
         <v>0.45</v>
       </c>
-      <c r="H185">
+      <c r="H185" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I185">
@@ -14757,7 +14769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>26</v>
       </c>
@@ -14773,13 +14785,13 @@
       <c r="E186">
         <v>7</v>
       </c>
-      <c r="F186">
+      <c r="F186" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G186">
         <v>0.45</v>
       </c>
-      <c r="H186">
+      <c r="H186" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I186">
@@ -14850,13 +14862,13 @@
       <c r="E187">
         <v>7</v>
       </c>
-      <c r="F187">
+      <c r="F187" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G187">
         <v>0.45</v>
       </c>
-      <c r="H187">
+      <c r="H187" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I187">
@@ -14911,7 +14923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>26</v>
       </c>
@@ -14927,13 +14939,13 @@
       <c r="E188">
         <v>7</v>
       </c>
-      <c r="F188">
+      <c r="F188" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G188">
         <v>0.45</v>
       </c>
-      <c r="H188">
+      <c r="H188" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I188">
@@ -14988,7 +15000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>26</v>
       </c>
@@ -15004,13 +15016,13 @@
       <c r="E189">
         <v>7</v>
       </c>
-      <c r="F189">
+      <c r="F189" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G189">
         <v>0.45</v>
       </c>
-      <c r="H189">
+      <c r="H189" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I189">
@@ -15081,13 +15093,13 @@
       <c r="E190">
         <v>7</v>
       </c>
-      <c r="F190">
+      <c r="F190" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G190">
         <v>0.45</v>
       </c>
-      <c r="H190">
+      <c r="H190" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I190">
@@ -15158,13 +15170,13 @@
       <c r="E191">
         <v>7</v>
       </c>
-      <c r="F191">
+      <c r="F191" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G191">
         <v>0.45</v>
       </c>
-      <c r="H191">
+      <c r="H191" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I191">
@@ -15235,13 +15247,13 @@
       <c r="E192">
         <v>7</v>
       </c>
-      <c r="F192">
+      <c r="F192" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G192">
         <v>0.45</v>
       </c>
-      <c r="H192">
+      <c r="H192" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I192">
@@ -15312,13 +15324,13 @@
       <c r="E193">
         <v>7</v>
       </c>
-      <c r="F193">
+      <c r="F193" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G193">
         <v>0.45</v>
       </c>
-      <c r="H193">
+      <c r="H193" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I193">
@@ -15389,13 +15401,13 @@
       <c r="E194">
         <v>7</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G194">
         <v>0.45</v>
       </c>
-      <c r="H194">
+      <c r="H194" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I194">
@@ -15466,13 +15478,13 @@
       <c r="E195">
         <v>7</v>
       </c>
-      <c r="F195">
+      <c r="F195" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G195">
         <v>0.45</v>
       </c>
-      <c r="H195">
+      <c r="H195" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I195">
@@ -15543,13 +15555,13 @@
       <c r="E196">
         <v>7</v>
       </c>
-      <c r="F196">
+      <c r="F196" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G196">
         <v>0.45</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I196">
@@ -15604,7 +15616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>26</v>
       </c>
@@ -15620,13 +15632,13 @@
       <c r="E197">
         <v>7</v>
       </c>
-      <c r="F197">
+      <c r="F197" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G197">
         <v>0.45</v>
       </c>
-      <c r="H197">
+      <c r="H197" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I197">
@@ -15681,7 +15693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>26</v>
       </c>
@@ -15697,13 +15709,13 @@
       <c r="E198">
         <v>7</v>
       </c>
-      <c r="F198">
+      <c r="F198" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G198">
         <v>0.45</v>
       </c>
-      <c r="H198">
+      <c r="H198" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I198">
@@ -15774,13 +15786,13 @@
       <c r="E199">
         <v>7</v>
       </c>
-      <c r="F199">
+      <c r="F199" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G199">
         <v>0.45</v>
       </c>
-      <c r="H199">
+      <c r="H199" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I199">
@@ -15851,13 +15863,13 @@
       <c r="E200">
         <v>7</v>
       </c>
-      <c r="F200">
+      <c r="F200" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G200">
         <v>0.45</v>
       </c>
-      <c r="H200">
+      <c r="H200" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I200">
@@ -15928,13 +15940,13 @@
       <c r="E201">
         <v>7</v>
       </c>
-      <c r="F201">
+      <c r="F201" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G201">
         <v>0.45</v>
       </c>
-      <c r="H201">
+      <c r="H201" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I201">
@@ -16005,13 +16017,13 @@
       <c r="E202">
         <v>7</v>
       </c>
-      <c r="F202">
+      <c r="F202" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G202">
         <v>0.45</v>
       </c>
-      <c r="H202">
+      <c r="H202" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I202">
@@ -16082,13 +16094,13 @@
       <c r="E203">
         <v>7</v>
       </c>
-      <c r="F203">
+      <c r="F203" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G203">
         <v>0.45</v>
       </c>
-      <c r="H203">
+      <c r="H203" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I203">
@@ -16159,13 +16171,13 @@
       <c r="E204">
         <v>7</v>
       </c>
-      <c r="F204">
+      <c r="F204" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G204">
         <v>0.45</v>
       </c>
-      <c r="H204">
+      <c r="H204" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I204">
@@ -16236,13 +16248,13 @@
       <c r="E205">
         <v>7</v>
       </c>
-      <c r="F205">
+      <c r="F205" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G205">
         <v>0.45</v>
       </c>
-      <c r="H205">
+      <c r="H205" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I205">
@@ -16313,13 +16325,13 @@
       <c r="E206">
         <v>7</v>
       </c>
-      <c r="F206">
+      <c r="F206" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G206">
         <v>0.45</v>
       </c>
-      <c r="H206">
+      <c r="H206" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I206">
@@ -16390,13 +16402,13 @@
       <c r="E207">
         <v>7</v>
       </c>
-      <c r="F207">
+      <c r="F207" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G207">
         <v>0.45</v>
       </c>
-      <c r="H207">
+      <c r="H207" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I207">
@@ -16467,13 +16479,13 @@
       <c r="E208">
         <v>7</v>
       </c>
-      <c r="F208">
+      <c r="F208" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G208">
         <v>0.45</v>
       </c>
-      <c r="H208">
+      <c r="H208" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I208">
@@ -16528,7 +16540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -16544,13 +16556,13 @@
       <c r="E209">
         <v>7</v>
       </c>
-      <c r="F209">
+      <c r="F209" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G209">
         <v>0.45</v>
       </c>
-      <c r="H209">
+      <c r="H209" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I209">
@@ -16605,7 +16617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -16621,13 +16633,13 @@
       <c r="E210">
         <v>7</v>
       </c>
-      <c r="F210">
+      <c r="F210" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G210">
         <v>0.45</v>
       </c>
-      <c r="H210">
+      <c r="H210" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I210">
@@ -16698,13 +16710,13 @@
       <c r="E211">
         <v>7</v>
       </c>
-      <c r="F211">
+      <c r="F211" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G211">
         <v>0.45</v>
       </c>
-      <c r="H211">
+      <c r="H211" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I211">
@@ -16775,13 +16787,13 @@
       <c r="E212">
         <v>7</v>
       </c>
-      <c r="F212">
+      <c r="F212" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G212">
         <v>0.45</v>
       </c>
-      <c r="H212">
+      <c r="H212" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I212">
@@ -16852,13 +16864,13 @@
       <c r="E213">
         <v>7</v>
       </c>
-      <c r="F213">
+      <c r="F213" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G213">
         <v>0.45</v>
       </c>
-      <c r="H213">
+      <c r="H213" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I213">
@@ -16929,13 +16941,13 @@
       <c r="E214">
         <v>7</v>
       </c>
-      <c r="F214">
+      <c r="F214" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G214">
         <v>0.45</v>
       </c>
-      <c r="H214">
+      <c r="H214" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I214">
@@ -17006,13 +17018,13 @@
       <c r="E215">
         <v>7</v>
       </c>
-      <c r="F215">
+      <c r="F215" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G215">
         <v>0.45</v>
       </c>
-      <c r="H215">
+      <c r="H215" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I215">
@@ -17083,13 +17095,13 @@
       <c r="E216">
         <v>7</v>
       </c>
-      <c r="F216">
+      <c r="F216" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G216">
         <v>0.45</v>
       </c>
-      <c r="H216">
+      <c r="H216" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I216">
@@ -17160,13 +17172,13 @@
       <c r="E217">
         <v>7</v>
       </c>
-      <c r="F217">
+      <c r="F217" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G217">
         <v>0.45</v>
       </c>
-      <c r="H217">
+      <c r="H217" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I217">
@@ -17237,13 +17249,13 @@
       <c r="E218">
         <v>7</v>
       </c>
-      <c r="F218">
+      <c r="F218" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G218">
         <v>0.45</v>
       </c>
-      <c r="H218">
+      <c r="H218" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I218">
@@ -17298,7 +17310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>26</v>
       </c>
@@ -17314,13 +17326,13 @@
       <c r="E219">
         <v>7</v>
       </c>
-      <c r="F219">
+      <c r="F219" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G219">
         <v>0.45</v>
       </c>
-      <c r="H219">
+      <c r="H219" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I219">
@@ -17391,13 +17403,13 @@
       <c r="E220">
         <v>7</v>
       </c>
-      <c r="F220">
+      <c r="F220" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G220">
         <v>0.45</v>
       </c>
-      <c r="H220">
+      <c r="H220" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I220">
@@ -17468,13 +17480,13 @@
       <c r="E221">
         <v>7</v>
       </c>
-      <c r="F221">
+      <c r="F221" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G221">
         <v>0.45</v>
       </c>
-      <c r="H221">
+      <c r="H221" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I221">
@@ -17545,13 +17557,13 @@
       <c r="E222">
         <v>7</v>
       </c>
-      <c r="F222">
+      <c r="F222" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G222">
         <v>0.45</v>
       </c>
-      <c r="H222">
+      <c r="H222" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I222">
@@ -17622,13 +17634,13 @@
       <c r="E223">
         <v>7</v>
       </c>
-      <c r="F223">
+      <c r="F223" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G223">
         <v>0.45</v>
       </c>
-      <c r="H223">
+      <c r="H223" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I223">
@@ -17683,7 +17695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>26</v>
       </c>
@@ -17699,13 +17711,13 @@
       <c r="E224">
         <v>7</v>
       </c>
-      <c r="F224">
+      <c r="F224" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G224">
         <v>0.45</v>
       </c>
-      <c r="H224">
+      <c r="H224" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I224">
@@ -17776,13 +17788,13 @@
       <c r="E225">
         <v>7</v>
       </c>
-      <c r="F225">
+      <c r="F225" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G225">
         <v>0.45</v>
       </c>
-      <c r="H225">
+      <c r="H225" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I225">
@@ -17853,13 +17865,13 @@
       <c r="E226">
         <v>7</v>
       </c>
-      <c r="F226">
+      <c r="F226" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G226">
         <v>0.45</v>
       </c>
-      <c r="H226">
+      <c r="H226" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I226">
@@ -17930,13 +17942,13 @@
       <c r="E227">
         <v>7</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G227">
         <v>0.45</v>
       </c>
-      <c r="H227">
+      <c r="H227" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I227">
@@ -18007,13 +18019,13 @@
       <c r="E228">
         <v>7</v>
       </c>
-      <c r="F228">
+      <c r="F228" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G228">
         <v>0.45</v>
       </c>
-      <c r="H228">
+      <c r="H228" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I228">
@@ -18084,13 +18096,13 @@
       <c r="E229">
         <v>7</v>
       </c>
-      <c r="F229">
+      <c r="F229" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G229">
         <v>0.45</v>
       </c>
-      <c r="H229">
+      <c r="H229" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I229">
@@ -18161,13 +18173,13 @@
       <c r="E230">
         <v>7</v>
       </c>
-      <c r="F230">
+      <c r="F230" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G230">
         <v>0.45</v>
       </c>
-      <c r="H230">
+      <c r="H230" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I230">
@@ -18238,13 +18250,13 @@
       <c r="E231">
         <v>7</v>
       </c>
-      <c r="F231">
+      <c r="F231" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G231">
         <v>0.45</v>
       </c>
-      <c r="H231">
+      <c r="H231" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I231">
@@ -18315,13 +18327,13 @@
       <c r="E232">
         <v>7</v>
       </c>
-      <c r="F232">
+      <c r="F232" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G232">
         <v>0.45</v>
       </c>
-      <c r="H232">
+      <c r="H232" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I232">
@@ -18376,7 +18388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>26</v>
       </c>
@@ -18392,13 +18404,13 @@
       <c r="E233">
         <v>7</v>
       </c>
-      <c r="F233">
+      <c r="F233" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G233">
         <v>0.45</v>
       </c>
-      <c r="H233">
+      <c r="H233" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I233">
@@ -18469,13 +18481,13 @@
       <c r="E234">
         <v>7</v>
       </c>
-      <c r="F234">
+      <c r="F234" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G234">
         <v>0.45</v>
       </c>
-      <c r="H234">
+      <c r="H234" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I234">
@@ -18546,13 +18558,13 @@
       <c r="E235">
         <v>7</v>
       </c>
-      <c r="F235">
+      <c r="F235" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G235">
         <v>0.45</v>
       </c>
-      <c r="H235">
+      <c r="H235" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I235">
@@ -18623,13 +18635,13 @@
       <c r="E236">
         <v>7</v>
       </c>
-      <c r="F236">
+      <c r="F236" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G236">
         <v>0.45</v>
       </c>
-      <c r="H236">
+      <c r="H236" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I236">
@@ -18700,13 +18712,13 @@
       <c r="E237">
         <v>7</v>
       </c>
-      <c r="F237">
+      <c r="F237" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G237">
         <v>0.45</v>
       </c>
-      <c r="H237">
+      <c r="H237" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I237">
@@ -18777,13 +18789,13 @@
       <c r="E238">
         <v>7</v>
       </c>
-      <c r="F238">
+      <c r="F238" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G238">
         <v>0.45</v>
       </c>
-      <c r="H238">
+      <c r="H238" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I238">
@@ -18854,13 +18866,13 @@
       <c r="E239">
         <v>7</v>
       </c>
-      <c r="F239">
+      <c r="F239" s="4">
         <v>18.202853409815891</v>
       </c>
       <c r="G239">
         <v>0.45</v>
       </c>
-      <c r="H239">
+      <c r="H239" s="4">
         <v>6.8042518700701224</v>
       </c>
       <c r="I239">
@@ -18915,7 +18927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>27</v>
       </c>
@@ -18992,7 +19004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>27</v>
       </c>
@@ -19069,7 +19081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>27</v>
       </c>
@@ -19146,7 +19158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>27</v>
       </c>
@@ -19223,7 +19235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>27</v>
       </c>
@@ -19300,7 +19312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>27</v>
       </c>
@@ -19377,7 +19389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>27</v>
       </c>
@@ -19454,7 +19466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>27</v>
       </c>
@@ -19531,7 +19543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>27</v>
       </c>
@@ -19608,7 +19620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>27</v>
       </c>
@@ -19685,7 +19697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>27</v>
       </c>
@@ -19762,7 +19774,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>27</v>
       </c>
@@ -19839,7 +19851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>27</v>
       </c>
@@ -19916,7 +19928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>27</v>
       </c>
@@ -19993,7 +20005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>27</v>
       </c>
@@ -20070,7 +20082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>27</v>
       </c>
@@ -20147,7 +20159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>27</v>
       </c>
@@ -20224,7 +20236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>27</v>
       </c>
@@ -20301,7 +20313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>27</v>
       </c>
@@ -20378,7 +20390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>27</v>
       </c>
@@ -20455,7 +20467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>27</v>
       </c>
@@ -20532,7 +20544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>27</v>
       </c>
@@ -20609,7 +20621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>27</v>
       </c>
@@ -20686,7 +20698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>27</v>
       </c>
@@ -20763,7 +20775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>27</v>
       </c>
@@ -20840,7 +20852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>27</v>
       </c>
@@ -20917,7 +20929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>27</v>
       </c>
@@ -20994,7 +21006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>27</v>
       </c>
@@ -21071,7 +21083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>27</v>
       </c>
@@ -21148,7 +21160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>27</v>
       </c>
@@ -21225,7 +21237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>27</v>
       </c>
@@ -21302,7 +21314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>27</v>
       </c>
@@ -21379,7 +21391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>27</v>
       </c>
@@ -21456,7 +21468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>27</v>
       </c>
@@ -21533,7 +21545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>27</v>
       </c>
@@ -21610,7 +21622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>27</v>
       </c>
@@ -21687,7 +21699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>27</v>
       </c>
@@ -21764,7 +21776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>27</v>
       </c>
@@ -21841,7 +21853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>27</v>
       </c>
@@ -21918,7 +21930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>27</v>
       </c>
@@ -21995,7 +22007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>27</v>
       </c>
@@ -22072,7 +22084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>27</v>
       </c>
@@ -22149,7 +22161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>27</v>
       </c>
@@ -22226,7 +22238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>27</v>
       </c>
@@ -22303,7 +22315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>27</v>
       </c>
@@ -22380,7 +22392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>27</v>
       </c>
@@ -22457,7 +22469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>27</v>
       </c>
@@ -22534,7 +22546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>27</v>
       </c>
@@ -22611,7 +22623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>27</v>
       </c>
@@ -22688,7 +22700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>27</v>
       </c>
@@ -22765,7 +22777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>27</v>
       </c>
@@ -22842,7 +22854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>27</v>
       </c>
@@ -22919,7 +22931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>27</v>
       </c>
@@ -22996,7 +23008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>27</v>
       </c>
@@ -23073,7 +23085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>27</v>
       </c>
@@ -23150,7 +23162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>27</v>
       </c>
@@ -23227,7 +23239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>27</v>
       </c>
@@ -23304,7 +23316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>27</v>
       </c>
@@ -23381,7 +23393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>27</v>
       </c>
@@ -23458,7 +23470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>27</v>
       </c>
@@ -23535,7 +23547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>27</v>
       </c>
@@ -23612,7 +23624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>27</v>
       </c>
@@ -23689,7 +23701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>27</v>
       </c>
@@ -23766,7 +23778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>27</v>
       </c>
@@ -23843,7 +23855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>27</v>
       </c>
@@ -23920,7 +23932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>27</v>
       </c>
@@ -23997,7 +24009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>27</v>
       </c>
@@ -24074,7 +24086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>27</v>
       </c>
@@ -24151,7 +24163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>27</v>
       </c>
@@ -24228,7 +24240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>27</v>
       </c>
@@ -24305,7 +24317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>27</v>
       </c>
@@ -24382,7 +24394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>27</v>
       </c>
@@ -24459,7 +24471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>27</v>
       </c>
@@ -24536,7 +24548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>27</v>
       </c>
@@ -24613,7 +24625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>27</v>
       </c>
@@ -24690,7 +24702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>27</v>
       </c>
@@ -24767,7 +24779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>27</v>
       </c>
@@ -24844,7 +24856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>27</v>
       </c>
@@ -24921,7 +24933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>27</v>
       </c>
@@ -24998,7 +25010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>27</v>
       </c>
@@ -25075,7 +25087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>27</v>
       </c>
@@ -25152,7 +25164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>27</v>
       </c>
@@ -25229,7 +25241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>27</v>
       </c>
@@ -25306,7 +25318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>27</v>
       </c>
@@ -25383,7 +25395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>27</v>
       </c>
@@ -25460,7 +25472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>27</v>
       </c>
@@ -25537,7 +25549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>27</v>
       </c>
@@ -25614,7 +25626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>27</v>
       </c>
@@ -25691,7 +25703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>27</v>
       </c>
@@ -25768,7 +25780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>27</v>
       </c>
@@ -25845,7 +25857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>27</v>
       </c>
@@ -25922,7 +25934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>27</v>
       </c>
@@ -25999,7 +26011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>27</v>
       </c>
@@ -26076,7 +26088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>27</v>
       </c>
@@ -26153,7 +26165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>27</v>
       </c>
@@ -26230,7 +26242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>27</v>
       </c>
@@ -26307,7 +26319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>27</v>
       </c>
@@ -26384,7 +26396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>27</v>
       </c>
@@ -26461,7 +26473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>27</v>
       </c>
@@ -26538,7 +26550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>27</v>
       </c>
@@ -26615,7 +26627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>27</v>
       </c>
@@ -26692,7 +26704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>27</v>
       </c>
@@ -26769,7 +26781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>27</v>
       </c>
@@ -26846,7 +26858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>27</v>
       </c>
@@ -26923,7 +26935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>27</v>
       </c>
@@ -27000,7 +27012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>27</v>
       </c>
@@ -27077,7 +27089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>27</v>
       </c>
@@ -27154,7 +27166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>27</v>
       </c>
@@ -27231,7 +27243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>27</v>
       </c>
@@ -27308,7 +27320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>27</v>
       </c>
@@ -27385,7 +27397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>27</v>
       </c>
@@ -27462,7 +27474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>27</v>
       </c>
@@ -27539,7 +27551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>27</v>
       </c>
@@ -27616,7 +27628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>27</v>
       </c>
@@ -27693,7 +27705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>27</v>
       </c>
@@ -27770,7 +27782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>27</v>
       </c>
@@ -27847,7 +27859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>27</v>
       </c>
@@ -27924,7 +27936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>27</v>
       </c>
@@ -28001,7 +28013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>27</v>
       </c>
@@ -28078,7 +28090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>27</v>
       </c>
@@ -37245,12 +37257,7 @@
   <autoFilter ref="A1:Y477" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="PRD85_PR40_CPent_UD045_UR045_PE80_I0"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="VERDADERO"/>
+        <filter val="PRD85_PR40_CPent_UD035_UR045_PE80_I0"/>
       </filters>
     </filterColumn>
   </autoFilter>
